--- a/en/downloads/data-excel/12.4.2.xlsx
+++ b/en/downloads/data-excel/12.4.2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -242,7 +242,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -330,6 +330,15 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -636,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="38.7109375" customWidth="1"/>
@@ -645,7 +654,7 @@
     <col min="8" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
@@ -661,7 +670,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="2"/>
     </row>
-    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
@@ -671,7 +680,7 @@
       <c r="G2" s="6"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
@@ -711,8 +720,11 @@
       <c r="M3" s="9">
         <v>2023</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" s="30" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N3" s="31">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="30" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>11</v>
       </c>
@@ -754,8 +766,12 @@
       <c r="M4" s="29">
         <v>1963.9481143272037</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N4" s="32">
+        <f>N5/N6*1000</f>
+        <v>2042.705930870156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>9</v>
       </c>
@@ -795,8 +811,11 @@
       <c r="M5" s="23">
         <v>14065.6</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N5" s="33">
+        <v>13373.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>10</v>
       </c>
@@ -836,8 +855,11 @@
       <c r="M6" s="22">
         <v>7161.9</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="24" x14ac:dyDescent="0.25">
+      <c r="N6" s="33">
+        <v>6547.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="24" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>15</v>
       </c>
@@ -877,8 +899,11 @@
       <c r="M7" s="22">
         <v>46.213456944602434</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N7" s="22">
+        <v>52.342897416571645</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>18</v>
       </c>
@@ -918,8 +943,11 @@
       <c r="M8" s="19">
         <v>4.4790126265498803E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N8" s="19">
+        <v>3.4070578056031614E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -929,7 +957,7 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -939,7 +967,7 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -949,7 +977,7 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -959,7 +987,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -969,7 +997,7 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -979,7 +1007,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -989,7 +1017,7 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
